--- a/docs/software-engineering/Rentino-Phase1-References.xlsx
+++ b/docs/software-engineering/Rentino-Phase1-References.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="References" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'References'!$A$1:$D$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'References'!$A$1:$D$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1164,8 +1164,108 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>[35]</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>W. G. Cochran, Sampling Techniques, 3rd ed. New York: Wiley, 1977.</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>تکمیلی</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>[36]</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>C. H. Lawshe, “A quantitative approach to content validity,” Personnel Psychology, vol. 28, no. 4, pp. 563-575, 1975, doi: 10.1111/j.1744-6570.1975.tb01393.x.</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>تکمیلی</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>[37]</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>L. J. Cronbach, “Coefficient alpha and the internal structure of tests,” Psychometrika, vol. 16, no. 3, pp. 297-334, 1951, doi: 10.1007/BF02310555.</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>تکمیلی</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>[38]</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>R. Likert, “A technique for the measurement of attitudes,” Archives of Psychology, vol. 22, no. 140, pp. 5-55, 1932.</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>تکمیلی</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>[39]</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>R. V. Krejcie and D. W. Morgan, “Determining sample size for research activities,” Educational and Psychological Measurement, vol. 30, no. 3, pp. 607-610, 1970, doi: 10.1177/001316447003000308.</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>تکمیلی</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D35"/>
+  <autoFilter ref="A1:D40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>